--- a/tests/workbooks/test_calendars.xlsx
+++ b/tests/workbooks/test_calendars.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8D9F99-DE43-410A-A43C-82058957EFB4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6823EF69-2FA7-417C-B09F-FDA6AD3CCA6D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{93E3CEBE-2A7E-45F9-A944-9E4960940BAD}"/>
   </bookViews>
@@ -16,6 +16,8 @@
     <sheet name="types" sheetId="1" r:id="rId1"/>
     <sheet name="functions" sheetId="2" r:id="rId2"/>
     <sheet name="addremove holidays" sheetId="6" r:id="rId3"/>
+    <sheet name="adjust , advance" sheetId="7" r:id="rId4"/>
+    <sheet name="joined calendar" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="78">
   <si>
     <t>ARGENTINA</t>
   </si>
@@ -158,9 +160,6 @@
     <t>WEEKENDSONLY</t>
   </si>
   <si>
-    <t>JOINTCALENDAR</t>
-  </si>
-  <si>
     <t>UNKNOWN_KEY</t>
   </si>
   <si>
@@ -228,6 +227,42 @@
   </si>
   <si>
     <t>qlWeekday</t>
+  </si>
+  <si>
+    <t>Following</t>
+  </si>
+  <si>
+    <t># of time_units</t>
+  </si>
+  <si>
+    <t>time_unit</t>
+  </si>
+  <si>
+    <t>period</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+  <si>
+    <t>DAYS</t>
+  </si>
+  <si>
+    <t>qlCalendarAdjust</t>
+  </si>
+  <si>
+    <t>qlCalendarAdvance</t>
+  </si>
+  <si>
+    <t>businessday_convention</t>
+  </si>
+  <si>
+    <t>calender_rule</t>
+  </si>
+  <si>
+    <t>JOINHOLIDAYS</t>
+  </si>
+  <si>
+    <t>qlCalender</t>
   </si>
 </sst>
 </file>
@@ -591,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3075420B-A904-48C0-8CC0-21FB5C882A54}">
-  <dimension ref="B2:C46"/>
+  <dimension ref="B2:C45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="37.140625" customWidth="1"/>
@@ -602,447 +637,396 @@
       <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="str">
-        <f>_xll.qlCalendar(B2)</f>
-        <v>Buenos Aires stock exchange</v>
+      <c r="C2" t="e">
+        <f ca="1">_xll.qlCalendar(B2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="str">
-        <f>_xll.qlCalendar(B3)</f>
-        <v>Australia settlement</v>
+      <c r="C3" t="e">
+        <f ca="1">_xll.qlCalendar(B3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" t="str">
-        <f>_xll.qlCalendar(B4)</f>
-        <v>Austrian settlement</v>
+      <c r="C4" t="e">
+        <f ca="1">_xll.qlCalendar(B4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>3</v>
       </c>
-      <c r="C5" t="str">
-        <f>_xll.qlCalendar(B5)</f>
-        <v>Botswana</v>
+      <c r="C5" t="e">
+        <f ca="1">_xll.qlCalendar(B5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="str">
-        <f>_xll.qlCalendar(B6)</f>
-        <v>Brazil</v>
+      <c r="C6" t="e">
+        <f ca="1">_xll.qlCalendar(B6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" t="str">
-        <f>_xll.qlCalendar(B7)</f>
-        <v>Canada</v>
+      <c r="C7" t="e">
+        <f ca="1">_xll.qlCalendar(B7)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>6</v>
       </c>
-      <c r="C8" t="str">
-        <f>_xll.qlCalendar(B8)</f>
-        <v>Santiago Stock Exchange</v>
+      <c r="C8" t="e">
+        <f ca="1">_xll.qlCalendar(B8)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" t="str">
-        <f>_xll.qlCalendar(B9)</f>
-        <v>Shanghai stock exchange</v>
+      <c r="C9" t="e">
+        <f ca="1">_xll.qlCalendar(B9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" t="str">
-        <f>_xll.qlCalendar(B10)</f>
-        <v>Prague stock exchange</v>
+      <c r="C10" t="e">
+        <f ca="1">_xll.qlCalendar(B10)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="C11" t="str">
-        <f>_xll.qlCalendar(B11)</f>
-        <v>Denmark</v>
+      <c r="C11" t="e">
+        <f ca="1">_xll.qlCalendar(B11)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>10</v>
       </c>
-      <c r="C12" t="str">
-        <f>_xll.qlCalendar(B12)</f>
-        <v>Finland</v>
+      <c r="C12" t="e">
+        <f ca="1">_xll.qlCalendar(B12)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>11</v>
       </c>
-      <c r="C13" t="str">
-        <f>_xll.qlCalendar(B13)</f>
-        <v>French settlement</v>
+      <c r="C13" t="e">
+        <f ca="1">_xll.qlCalendar(B13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>12</v>
       </c>
-      <c r="C14" t="str">
-        <f>_xll.qlCalendar(B14)</f>
-        <v>Frankfurt stock exchange</v>
+      <c r="C14" t="e">
+        <f ca="1">_xll.qlCalendar(B14)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="C15" t="str">
-        <f>_xll.qlCalendar(B15)</f>
-        <v>Hong Kong stock exchange</v>
+      <c r="C15" t="e">
+        <f ca="1">_xll.qlCalendar(B15)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>14</v>
       </c>
-      <c r="C16" t="str">
-        <f>_xll.qlCalendar(B16)</f>
-        <v>Hungary</v>
+      <c r="C16" t="e">
+        <f ca="1">_xll.qlCalendar(B16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>15</v>
       </c>
-      <c r="C17" t="str">
-        <f>_xll.qlCalendar(B17)</f>
-        <v>Iceland stock exchange</v>
+      <c r="C17" t="e">
+        <f ca="1">_xll.qlCalendar(B17)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>16</v>
       </c>
-      <c r="C18" t="str">
-        <f>_xll.qlCalendar(B18)</f>
-        <v>National Stock Exchange of India</v>
+      <c r="C18" t="e">
+        <f ca="1">_xll.qlCalendar(B18)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>17</v>
       </c>
-      <c r="C19" t="str">
-        <f>_xll.qlCalendar(B19)</f>
-        <v>Jakarta stock exchange</v>
+      <c r="C19" t="e">
+        <f ca="1">_xll.qlCalendar(B19)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>18</v>
       </c>
-      <c r="C20" t="str">
-        <f>_xll.qlCalendar(B20)</f>
-        <v>Tel Aviv stock exchange</v>
+      <c r="C20" t="e">
+        <f ca="1">_xll.qlCalendar(B20)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>19</v>
       </c>
-      <c r="C21" t="str">
-        <f>_xll.qlCalendar(B21)</f>
-        <v>Italian settlement</v>
+      <c r="C21" t="e">
+        <f ca="1">_xll.qlCalendar(B21)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>20</v>
       </c>
-      <c r="C22" t="str">
-        <f>_xll.qlCalendar(B22)</f>
-        <v>Japan</v>
+      <c r="C22" t="e">
+        <f ca="1">_xll.qlCalendar(B22)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>21</v>
       </c>
-      <c r="C23" t="str">
-        <f>_xll.qlCalendar(B23)</f>
-        <v>Mexican stock exchange</v>
+      <c r="C23" t="e">
+        <f ca="1">_xll.qlCalendar(B23)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>22</v>
       </c>
-      <c r="C24" t="str">
-        <f>_xll.qlCalendar(B24)</f>
-        <v>New Zealand (Wellington)</v>
+      <c r="C24" t="e">
+        <f ca="1">_xll.qlCalendar(B24)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>23</v>
       </c>
-      <c r="C25" t="str">
-        <f>_xll.qlCalendar(B25)</f>
-        <v>Norway</v>
+      <c r="C25" t="e">
+        <f ca="1">_xll.qlCalendar(B25)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>24</v>
       </c>
-      <c r="C26" t="str">
-        <f>_xll.qlCalendar(B26)</f>
-        <v>Poland Settlement</v>
+      <c r="C26" t="e">
+        <f ca="1">_xll.qlCalendar(B26)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>25</v>
       </c>
-      <c r="C27" t="str">
-        <f>_xll.qlCalendar(B27)</f>
-        <v>Bucharest stock exchange</v>
+      <c r="C27" t="e">
+        <f ca="1">_xll.qlCalendar(B27)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>26</v>
       </c>
-      <c r="C28" t="str">
-        <f>_xll.qlCalendar(B28)</f>
-        <v>Russian settlement</v>
+      <c r="C28" t="e">
+        <f ca="1">_xll.qlCalendar(B28)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>27</v>
       </c>
-      <c r="C29" t="str">
-        <f>_xll.qlCalendar(B29)</f>
-        <v>Tadawul</v>
+      <c r="C29" t="e">
+        <f ca="1">_xll.qlCalendar(B29)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>28</v>
       </c>
-      <c r="C30" t="str">
-        <f>_xll.qlCalendar(B30)</f>
-        <v>Singapore exchange</v>
+      <c r="C30" t="e">
+        <f ca="1">_xll.qlCalendar(B30)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>29</v>
       </c>
-      <c r="C31" t="str">
-        <f>_xll.qlCalendar(B31)</f>
-        <v>Bratislava stock exchange</v>
+      <c r="C31" t="e">
+        <f ca="1">_xll.qlCalendar(B31)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>30</v>
       </c>
-      <c r="C32" t="str">
-        <f>_xll.qlCalendar(B32)</f>
-        <v>South Africa</v>
+      <c r="C32" t="e">
+        <f ca="1">_xll.qlCalendar(B32)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>31</v>
       </c>
-      <c r="C33" t="str">
-        <f>_xll.qlCalendar(B33)</f>
-        <v>South-Korea exchange</v>
+      <c r="C33" t="e">
+        <f ca="1">_xll.qlCalendar(B33)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>32</v>
       </c>
-      <c r="C34" t="str">
-        <f>_xll.qlCalendar(B34)</f>
-        <v>Sweden</v>
+      <c r="C34" t="e">
+        <f ca="1">_xll.qlCalendar(B34)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>33</v>
       </c>
-      <c r="C35" t="str">
-        <f>_xll.qlCalendar(B35)</f>
-        <v>Switzerland</v>
+      <c r="C35" t="e">
+        <f ca="1">_xll.qlCalendar(B35)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>34</v>
       </c>
-      <c r="C36" t="str">
-        <f>_xll.qlCalendar(B36)</f>
-        <v>Taiwan stock exchange</v>
+      <c r="C36" t="e">
+        <f ca="1">_xll.qlCalendar(B36)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>35</v>
       </c>
-      <c r="C37" t="str">
-        <f>_xll.qlCalendar(B37)</f>
-        <v>TARGET</v>
+      <c r="C37" t="e">
+        <f ca="1">_xll.qlCalendar(B37)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>36</v>
       </c>
-      <c r="C38" t="str">
-        <f>_xll.qlCalendar(B38)</f>
-        <v>Thailand stock exchange</v>
+      <c r="C38" t="e">
+        <f ca="1">_xll.qlCalendar(B38)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>37</v>
       </c>
-      <c r="C39" t="str">
-        <f>_xll.qlCalendar(B39)</f>
-        <v>Turkey</v>
+      <c r="C39" t="e">
+        <f ca="1">_xll.qlCalendar(B39)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>38</v>
       </c>
-      <c r="C40" t="str">
-        <f>_xll.qlCalendar(B40)</f>
-        <v>Ukrainian stock exchange</v>
+      <c r="C40" t="e">
+        <f ca="1">_xll.qlCalendar(B40)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C41" t="str">
-        <f>_xll.qlCalendar(B41)</f>
-        <v xml:space="preserve">TypeError: TypeError: UnitedStates.__init__() missing 1 required positional argument: 'm'
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlibxloil\calendars.py", line 107, in qlCalendar
-    return _calendars_by_name(calendar_name)
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlibxloil\calendars.py", line 87, in _calendars_by_name
-    return calendar()
-TypeError: UnitedStates.__init__() missing 1 required positional argument: 'm'
-</v>
+      <c r="C41" t="e">
+        <f ca="1">_xll.qlCalendar(B41)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>40</v>
       </c>
-      <c r="C42" t="str">
-        <f>_xll.qlCalendar(B42)</f>
-        <v>UK settlement</v>
+      <c r="C42" t="e">
+        <f ca="1">_xll.qlCalendar(B42)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>41</v>
       </c>
-      <c r="C43" t="str">
-        <f>_xll.qlCalendar(B43)</f>
-        <v>Null</v>
+      <c r="C43" t="e">
+        <f ca="1">_xll.qlCalendar(B43)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>42</v>
       </c>
-      <c r="C44" t="str">
-        <f>_xll.qlCalendar(B44)</f>
-        <v>weekends only</v>
+      <c r="C44" t="e">
+        <f ca="1">_xll.qlCalendar(B44)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="1" t="s">
+      <c r="B45" t="s">
         <v>43</v>
       </c>
-      <c r="C45" t="str">
-        <f>_xll.qlCalendar(B45)</f>
-        <v xml:space="preserve">TypeError: TypeError: Wrong number or type of arguments for overloaded function 'new_JointCalendar'.
-  Possible C/C++ prototypes are:
-    QuantLib::JointCalendar::JointCalendar(Calendar const &amp;,Calendar const &amp;,JointCalendarRule)
-    QuantLib::JointCalendar::JointCalendar(Calendar const &amp;,Calendar const &amp;)
-    QuantLib::JointCalendar::JointCalendar(Calendar const &amp;,Calendar const &amp;,Calendar const &amp;,JointCalendarRule)
-    QuantLib::JointCalendar::JointCalendar(Calendar const &amp;,Calendar const &amp;,Calendar const &amp;)
-    QuantLib::JointCalendar::JointCalendar(Calendar const &amp;,Calendar const &amp;,Calendar const &amp;,Calendar const &amp;,JointCalendarRule)
-    QuantLib::JointCalendar::JointCalendar(Calendar const &amp;,Calendar const &amp;,Calendar const &amp;,Calendar const &amp;)
-    QuantLib::JointCalendar::JointCalendar(std::vector&lt; Calendar,std::allocator&lt; Calendar &gt; &gt; const &amp;,JointCalendarRule)
-    QuantLib::JointCalendar::JointCalendar(std::vector&lt; Calendar,std::allocator&lt; Calendar &gt; &gt; const &amp;)
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlibxloil\calendars.py", line 107, in qlCalendar
-    return _calendars_by_name(calendar_name)
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlibxloil\calendars.py", line 87, in _calendars_by_name
-    return calendar()
-  File "C:\Users\kerst\.conda\envs\qlxloil\Lib\site-packages\QuantLib\QuantLib.py", line 3619, in __init__
-    _QuantLib.JointCalendar_swiginit(self, _QuantLib.new_JointCalendar(*args))
-                                           ~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^
-TypeError: Wrong number or type of arguments for overloaded function 'new_JointCalendar'.
-  Possible C/C++ prototypes are:
-    QuantLib::JointCalendar::JointCalendar(Calendar const &amp;,Calendar const &amp;,JointCalendarRule)
-    QuantLib::JointCalendar::JointCalendar(Calendar const &amp;,Calendar const &amp;)
-    QuantLib::JointCalendar::JointCalendar(Calendar const &amp;,Calendar const &amp;,Calendar const &amp;,JointCalendarRule)
-    QuantLib::JointCalendar::JointCalendar(Calendar const &amp;,Calendar const &amp;,Calendar const &amp;)
-    QuantLib::JointCalendar::JointCalendar(Calendar const &amp;,Calendar const &amp;,Calendar const &amp;,Calendar const &amp;,JointCalendarRule)
-    QuantLib::JointCalendar::JointCalendar(Calendar const &amp;,Calendar const &amp;,Calendar const &amp;,Calendar const &amp;)
-    QuantLib::JointCalendar::JointCalendar(std::vector&lt; Calendar,std::allocator&lt; Calendar &gt; &gt; const &amp;,JointCalendarRule)
-    QuantLib::JointCalendar::JointCalendar(std::vector&lt; Calendar,std::allocator&lt; Calendar &gt; &gt; const &amp;)
-</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" t="s">
-        <v>44</v>
-      </c>
-      <c r="C46" t="str">
-        <f>_xll.qlCalendar(B46)</f>
-        <v xml:space="preserve">ValueError: ValueError: Unknown calendar: UNKNOWN_KEY
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlibxloil\calendars.py", line 107, in qlCalendar
-    return _calendars_by_name(calendar_name)
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlibxloil\calendars.py", line 86, in _calendars_by_name
-    raise ValueError(f"Unknown calendar: {name}")
-ValueError: Unknown calendar: UNKNOWN_KEY
-</v>
+      <c r="C45" t="e">
+        <f ca="1">_xll.qlCalendar(B45)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -1062,16 +1046,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" t="str">
-        <f>_xll.qlCalendar("TARGET")</f>
-        <v>TARGET</v>
+        <v>59</v>
+      </c>
+      <c r="B1" t="e">
+        <f ca="1">_xll.qlCalendar("TARGET")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B2" s="2">
         <v>46171</v>
@@ -1079,16 +1063,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" t="str">
-        <f>_xll.qlDateWeekday(B2)</f>
-        <v>FRIDAY</v>
+        <v>65</v>
+      </c>
+      <c r="B3" t="e">
+        <f ca="1">_xll.qlDateWeekday(B2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="2">
         <v>46023</v>
@@ -1096,7 +1080,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" s="2">
         <v>46027</v>
@@ -1104,165 +1088,172 @@
       <c r="D5" s="2">
         <v>46025</v>
       </c>
-      <c r="E5" t="b">
-        <f>_xll.qlCalendarIsBusinessDay(B1,D5)</f>
-        <v>0</v>
+      <c r="E5" t="e">
+        <f ca="1">_xll.qlCalendarIsBusinessDay(B1,D5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E6" t="b">
-        <f>_xll.qlCalendarIsHoliday(B1,D5)</f>
-        <v>1</v>
+      <c r="E6" t="e">
+        <f ca="1">_xll.qlCalendarIsHoliday(B1,D5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" t="b">
-        <f>_xll.qlCalendarisWeekend($B$1,B3)</f>
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="B7" t="e">
+        <f ca="1">_xll.qlCalendarisWeekend($B$1,B3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="2">
-        <f>_xll.qlCalendarStartOfMonth(B1,B2)</f>
-        <v>46146</v>
+        <v>45</v>
+      </c>
+      <c r="B8" s="2" t="e">
+        <f ca="1">_xll.qlCalendarStartOfMonth(B1,B2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="2">
-        <f>_xll.qlCalendarEndOfMonth(B1,B2)</f>
-        <v>46171</v>
+        <v>46</v>
+      </c>
+      <c r="B9" s="2" t="e">
+        <f ca="1">_xll.qlCalendarEndOfMonth(B1,B2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" t="b">
-        <f>_xll.qlCalendarIsBusinessDay(B1,B2)</f>
-        <v>1</v>
+        <v>47</v>
+      </c>
+      <c r="B10" t="e">
+        <f ca="1">_xll.qlCalendarIsBusinessDay(B1,B2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" t="b">
-        <f>_xll.qlCalendarIsHoliday(B1,B2)</f>
-        <v>0</v>
+        <v>48</v>
+      </c>
+      <c r="B11" t="e">
+        <f ca="1">_xll.qlCalendarIsHoliday(B1,B2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" t="b">
-        <f>_xll.qlCalendarIsEndOfMonth(B1,B2)</f>
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="B12" t="e">
+        <f ca="1">_xll.qlCalendarIsEndOfMonth(B1,B2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" t="b">
-        <f>_xll.qlCalendarIsStartOfMonth(B1,B2)</f>
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="B13" t="e">
+        <f ca="1">_xll.qlCalendarIsStartOfMonth(B1,B2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14">
-        <f>_xll.qlCalendarBusinessDaysBetween(B1,B4,B5)</f>
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="B14" t="e">
+        <f ca="1">_xll.qlCalendarBusinessDaysBetween(B1,B4,B5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" t="str">
-        <f>_xll.qlCalendarName(B1)</f>
-        <v>TARGET</v>
+        <v>57</v>
+      </c>
+      <c r="B15" t="e">
+        <f ca="1">_xll.qlCalendarName(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" t="b">
-        <f>_xll.qlCalendarEmpty(B1)</f>
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="B16" t="e">
+        <f ca="1">_xll.qlCalendarEmpty(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="2">
-        <f t="array" ref="B17:B20">_xll.qlCalendarHolidayList(B1,B4,B5)</f>
-        <v>46023</v>
+        <v>55</v>
+      </c>
+      <c r="B17" s="2" t="e">
+        <f t="array" aca="1" ref="B17:B20" ca="1">_xll.qlCalendarHolidayList(B1,B4,B5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
-      <c r="B18" s="2">
-        <v>46023</v>
+      <c r="B18" s="2" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
-      <c r="B19" s="2">
-        <v>46023</v>
+      <c r="B19" s="2" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
-      <c r="B20" s="2">
-        <v>46023</v>
+      <c r="B20" s="2" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="2">
-        <f t="array" ref="B21:B25">_xll.qlCalendarBusinessDayList(B1,B4,B5)</f>
-        <v>46024</v>
+        <v>56</v>
+      </c>
+      <c r="B21" s="2" t="e">
+        <f t="array" aca="1" ref="B21:B25" ca="1">_xll.qlCalendarBusinessDayList(B1,B4,B5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
-      <c r="B22" s="2">
-        <v>46027</v>
+      <c r="B22" s="2" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" t="e">
-        <v>#N/A</v>
+        <f ca="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" t="e">
-        <v>#N/A</v>
+        <f ca="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" t="e">
-        <v>#N/A</v>
+        <f ca="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -1285,16 +1276,16 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" t="str">
-        <f>_xll.qlCalendar("TARGET")</f>
-        <v>TARGET</v>
+        <v>59</v>
+      </c>
+      <c r="B2" t="e">
+        <f ca="1">_xll.qlCalendar("TARGET")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B3" s="2">
         <v>46024</v>
@@ -1302,7 +1293,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="2">
         <v>46023</v>
@@ -1310,7 +1301,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B5" s="2">
         <v>46023</v>
@@ -1318,7 +1309,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6" s="2">
         <v>46027</v>
@@ -1326,89 +1317,248 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9" t="e">
-        <f>_xll.qlCalendarAddHoliday(B2,B3)</f>
-        <v>#N/A</v>
+        <f ca="1">_xll.qlCalendarAddHoliday(B2,B3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="2">
-        <f t="array" ref="B10:B12">_xll.qlCalendarHolidayList(B2,B5,B6)</f>
-        <v>46023</v>
+        <v>55</v>
+      </c>
+      <c r="B10" s="2" t="e">
+        <f t="array" aca="1" ref="B10:B12" ca="1">_xll.qlCalendarHolidayList(B2,B5,B6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="2">
-        <v>46024</v>
+      <c r="B11" s="2" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="e">
-        <v>#N/A</v>
+        <f ca="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" t="e">
-        <f>_xll.qlCalendarRemoveHoliday(B2,B4)</f>
-        <v>#N/A</v>
+        <f ca="1">_xll.qlCalendarRemoveHoliday(B2,B4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="2">
-        <f t="array" ref="B15:B17">_xll.qlCalendarHolidayList(B2,B5,B6)</f>
-        <v>46024</v>
+        <v>55</v>
+      </c>
+      <c r="B15" s="2" t="e">
+        <f t="array" aca="1" ref="B15:B17" ca="1">_xll.qlCalendarHolidayList(B2,B5,B6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="2">
-        <v>46024</v>
+      <c r="B16" s="2" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="2">
-        <v>46024</v>
+      <c r="B17" s="2" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" t="e">
-        <f>_xll.qlCalendarResetAddedAndRemovedHolidays(B2)</f>
-        <v>#N/A</v>
+        <f ca="1">_xll.qlCalendarResetAddedAndRemovedHolidays(B2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="2">
-        <f t="array" ref="B21:B23">_xll.qlCalendarHolidayList(B2,B5,B6)</f>
-        <v>46023</v>
+        <v>55</v>
+      </c>
+      <c r="B21" s="2" t="e">
+        <f t="array" aca="1" ref="B21:B23" ca="1">_xll.qlCalendarHolidayList(B2,B5,B6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="2">
-        <v>46023</v>
+      <c r="B22" s="2" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="2">
-        <v>46023</v>
+      <c r="B23" s="2" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92C2F300-0ACE-414A-85D4-FE4A0E362995}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" t="e">
+        <f ca="1">_xll.qlCalendar("TARGET")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46053</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="2" t="e">
+        <f ca="1">_xll.qlCalendarAdjust(B1,B2)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="2" t="e">
+        <f ca="1">_xll.qlCalendarAdvance(B1,B2,B4,B5,B3,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="2" t="e">
+        <f ca="1">_xll.qlCalendarAdvance2(B1,B2,B6,B3,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFBBB7C2-660D-4F66-9443-9DB0EA674324}">
+  <dimension ref="A3:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="2" width="49.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" t="e">
+        <f ca="1">_xll.qlCalendar("Sweden")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" t="e">
+        <f ca="1">_xll.qlCalendar("TARGET")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" t="e">
+        <f ca="1">_xll.qlCalendar("UnitedKingdom")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="e">
+        <f ca="1">_xll.qlCalendarJointCalendar(B3,B4,B6)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="e">
+        <f ca="1">_xll.qlCalendarJointCalendar2(B3,B4,B5)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>